--- a/3-能力管理/运行记录类文件/TXHS-03-03-运维服务能力管理指标体系.xlsx
+++ b/3-能力管理/运行记录类文件/TXHS-03-03-运维服务能力管理指标体系.xlsx
@@ -32,7 +32,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="126">
   <si>
-    <t xml:space="preserve">江西通信运维服务能力管理指标体系       </t>
+    <t xml:space="preserve">运维服务能力管理指标体系       </t>
   </si>
   <si>
     <t>编号</t>

--- a/3-能力管理/运行记录类文件/TXHS-03-03-运维服务能力管理指标体系.xlsx
+++ b/3-能力管理/运行记录类文件/TXHS-03-03-运维服务能力管理指标体系.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9575"/>
+    <workbookView windowWidth="21228" windowHeight="7787"/>
   </bookViews>
   <sheets>
     <sheet name="KPI指标体系" sheetId="1" r:id="rId1"/>
@@ -1223,7 +1223,7 @@
       <xdr:col>5</xdr:col>
       <xdr:colOff>2246630</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>283210</xdr:rowOff>
+      <xdr:rowOff>162560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1240,8 +1240,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3781425" y="824865"/>
-          <a:ext cx="2177415" cy="248920"/>
+          <a:off x="3781425" y="659765"/>
+          <a:ext cx="2177415" cy="128270"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1613,7 +1613,7 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
     </row>
-    <row r="2" ht="24" customHeight="1" spans="1:8">
+    <row r="2" ht="11" customHeight="1" spans="1:8">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1647,7 +1647,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" ht="24" customHeight="1" spans="1:8">
+    <row r="4" spans="1:8">
       <c r="A4" s="6">
         <f>ROW()-3</f>
         <v>1</v>
@@ -2337,7 +2337,9 @@
       </c>
     </row>
     <row r="32" ht="15.6" spans="1:8">
-      <c r="A32" s="6"/>
+      <c r="A32" s="6">
+        <v>29</v>
+      </c>
       <c r="B32" s="7"/>
       <c r="C32" s="9" t="s">
         <v>104</v>
@@ -2359,7 +2361,9 @@
       </c>
     </row>
     <row r="33" ht="15.6" spans="1:8">
-      <c r="A33" s="6"/>
+      <c r="A33" s="6">
+        <v>30</v>
+      </c>
       <c r="B33" s="7"/>
       <c r="C33" s="10"/>
       <c r="D33" s="8" t="s">
@@ -2520,7 +2524,7 @@
     <mergeCell ref="A1:H2"/>
   </mergeCells>
   <pageMargins left="0.707638888888889" right="0.511805555555556" top="0.747916666666667" bottom="0.747916666666667" header="0.313888888888889" footer="0.313888888888889"/>
-  <pageSetup paperSize="9" scale="10" fitToHeight="0" orientation="landscape"/>
+  <pageSetup paperSize="9" scale="92" fitToHeight="0" orientation="landscape"/>
   <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/3-能力管理/运行记录类文件/TXHS-03-03-运维服务能力管理指标体系.xlsx
+++ b/3-能力管理/运行记录类文件/TXHS-03-03-运维服务能力管理指标体系.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21228" windowHeight="7787"/>
+    <workbookView windowWidth="28515" windowHeight="12315"/>
   </bookViews>
   <sheets>
     <sheet name="KPI指标体系" sheetId="1" r:id="rId1"/>
@@ -490,7 +490,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -516,6 +516,13 @@
       <color indexed="8"/>
       <name val="宋体"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1046,65 +1053,65 @@
     </border>
   </borders>
   <cellStyleXfs count="55">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" applyNumberFormat="0" applyFont="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="8" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="7" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="9" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" applyNumberFormat="0" applyFont="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="8" applyNumberFormat="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="7" applyNumberFormat="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="9" applyNumberFormat="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
@@ -1240,7 +1247,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3781425" y="659765"/>
+          <a:off x="4193540" y="510540"/>
           <a:ext cx="2177415" cy="128270"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1589,19 +1596,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H38"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="4.75" customWidth="1"/>
     <col min="3" max="3" width="10.75" customWidth="1"/>
     <col min="4" max="4" width="21" customWidth="1"/>
-    <col min="5" max="5" width="8.62962962962963" customWidth="1"/>
-    <col min="6" max="6" width="64.6296296296296" customWidth="1"/>
+    <col min="5" max="5" width="8.625" customWidth="1"/>
+    <col min="6" max="6" width="64.625" customWidth="1"/>
     <col min="7" max="7" width="10.5" customWidth="1"/>
     <col min="8" max="8" width="17.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" customHeight="1" spans="1:8">
+    <row r="1" spans="1:8">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1623,7 +1630,7 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
     </row>
-    <row r="3" ht="24.75" customHeight="1" spans="1:8">
+    <row r="3" ht="13" customHeight="1" spans="1:8">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -2336,7 +2343,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="32" ht="15.6" spans="1:8">
+    <row r="32" ht="15" spans="1:8">
       <c r="A32" s="6">
         <v>29</v>
       </c>
@@ -2360,7 +2367,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="33" ht="15.6" spans="1:8">
+    <row r="33" ht="15" spans="1:8">
       <c r="A33" s="6">
         <v>30</v>
       </c>

--- a/3-能力管理/运行记录类文件/TXHS-03-03-运维服务能力管理指标体系.xlsx
+++ b/3-能力管理/运行记录类文件/TXHS-03-03-运维服务能力管理指标体系.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28515" windowHeight="12315"/>
+    <workbookView windowWidth="22188" windowHeight="9575"/>
   </bookViews>
   <sheets>
     <sheet name="KPI指标体系" sheetId="1" r:id="rId1"/>
@@ -77,7 +77,7 @@
     <t>≤2次</t>
   </si>
   <si>
-    <t>每年客户投诉数量</t>
+    <t>数量，所有项目客户投诉数量和</t>
   </si>
   <si>
     <t>年度</t>
@@ -158,16 +158,16 @@
     <t>绩效考核合格人数/绩效考核总人数*100%</t>
   </si>
   <si>
-    <t>技能评定</t>
-  </si>
-  <si>
-    <t>技能评定覆盖率</t>
+    <t>能力评价</t>
+  </si>
+  <si>
+    <t>能力评价覆盖率</t>
   </si>
   <si>
     <t>≥80%</t>
   </si>
   <si>
-    <t>实际进行技能评定的人数/应进行技能评定的人数*100%</t>
+    <t>实际进行能力评价的人数/应进行能力评价的人数*100%</t>
   </si>
   <si>
     <t>过程</t>
@@ -490,7 +490,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -516,13 +516,6 @@
       <color indexed="8"/>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -904,7 +897,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -925,6 +918,46 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1053,67 +1086,67 @@
     </border>
   </borders>
   <cellStyleXfs count="55">
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" applyNumberFormat="0" applyFont="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="8" applyNumberFormat="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="7" applyNumberFormat="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="9" applyNumberFormat="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" applyNumberFormat="0" applyFont="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="11" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="12" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="11" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="13" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1135,16 +1168,28 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="5" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1247,7 +1292,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4193540" y="510540"/>
+          <a:off x="3781425" y="521970"/>
           <a:ext cx="2177415" cy="128270"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1596,14 +1641,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H38"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="4.75" customWidth="1"/>
     <col min="3" max="3" width="10.75" customWidth="1"/>
     <col min="4" max="4" width="21" customWidth="1"/>
-    <col min="5" max="5" width="8.625" customWidth="1"/>
-    <col min="6" max="6" width="64.625" customWidth="1"/>
+    <col min="5" max="5" width="8.62962962962963" customWidth="1"/>
+    <col min="6" max="6" width="64.6296296296296" customWidth="1"/>
     <col min="7" max="7" width="10.5" customWidth="1"/>
     <col min="8" max="8" width="17.5" customWidth="1"/>
   </cols>
@@ -1662,114 +1707,114 @@
       <c r="B4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="8" t="s">
+      <c r="C4" s="8"/>
+      <c r="D4" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8" t="s">
+      <c r="F4" s="9"/>
+      <c r="G4" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="9" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="6">
-        <f t="shared" ref="A5:A14" si="0">ROW()-3</f>
+        <f>ROW()-3</f>
         <v>2</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="8" t="s">
+      <c r="B5" s="10"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="9" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="6">
-        <f t="shared" si="0"/>
+        <f>ROW()-3</f>
         <v>3</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="8" t="s">
+      <c r="B6" s="10"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="9" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="6">
-        <f t="shared" si="0"/>
+        <f>ROW()-3</f>
         <v>4</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="8" t="s">
+      <c r="B7" s="10"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="H7" s="9" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A8:A14" si="0">ROW()-3</f>
         <v>5</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G8" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1778,23 +1823,23 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7" t="s">
+      <c r="B9" s="12"/>
+      <c r="C9" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1803,23 +1848,23 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7" t="s">
+      <c r="B10" s="12"/>
+      <c r="C10" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="G10" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="H10" s="8" t="s">
+      <c r="H10" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1828,23 +1873,23 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7" t="s">
+      <c r="B11" s="12"/>
+      <c r="C11" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="G11" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="H11" s="8" t="s">
+      <c r="H11" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1852,23 +1897,23 @@
       <c r="A12" s="6">
         <v>9</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7" t="s">
+      <c r="B12" s="12"/>
+      <c r="C12" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="F12" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="G12" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="H12" s="8" t="s">
+      <c r="H12" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1877,23 +1922,23 @@
         <f>ROW()-3</f>
         <v>10</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7" t="s">
+      <c r="B13" s="12"/>
+      <c r="C13" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="G13" s="8" t="s">
+      <c r="G13" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H13" s="8" t="s">
+      <c r="H13" s="9" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1902,25 +1947,25 @@
         <f>ROW()-3</f>
         <v>11</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="G14" s="8" t="s">
+      <c r="G14" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H14" s="8" t="s">
+      <c r="H14" s="9" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1929,23 +1974,23 @@
         <f t="shared" ref="A15:A24" si="1">ROW()-3</f>
         <v>12</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7" t="s">
+      <c r="B15" s="12"/>
+      <c r="C15" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="F15" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="G15" s="8" t="s">
+      <c r="G15" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="H15" s="8" t="s">
+      <c r="H15" s="9" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1954,23 +1999,23 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7" t="s">
+      <c r="B16" s="12"/>
+      <c r="C16" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="E16" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="F16" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="G16" s="8" t="s">
+      <c r="G16" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="H16" s="8" t="s">
+      <c r="H16" s="9" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1979,23 +2024,23 @@
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7" t="s">
+      <c r="B17" s="12"/>
+      <c r="C17" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E17" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="F17" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="G17" s="8" t="s">
+      <c r="G17" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="H17" s="8" t="s">
+      <c r="H17" s="9" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2004,21 +2049,21 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8" t="s">
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="E18" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="F18" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G18" s="8" t="s">
+      <c r="G18" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="H18" s="8" t="s">
+      <c r="H18" s="9" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2027,23 +2072,23 @@
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7" t="s">
+      <c r="B19" s="12"/>
+      <c r="C19" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="E19" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F19" s="8" t="s">
+      <c r="F19" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="G19" s="8" t="s">
+      <c r="G19" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="H19" s="8" t="s">
+      <c r="H19" s="9" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2052,21 +2097,21 @@
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="8" t="s">
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="E20" s="8" t="s">
+      <c r="E20" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="F20" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="G20" s="8" t="s">
+      <c r="G20" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="H20" s="8" t="s">
+      <c r="H20" s="9" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2075,23 +2120,23 @@
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7" t="s">
+      <c r="B21" s="12"/>
+      <c r="C21" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="E21" s="8" t="s">
+      <c r="E21" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="F21" s="8" t="s">
+      <c r="F21" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="G21" s="8" t="s">
+      <c r="G21" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="H21" s="8" t="s">
+      <c r="H21" s="9" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2100,23 +2145,23 @@
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7" t="s">
+      <c r="B22" s="12"/>
+      <c r="C22" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D22" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="E22" s="8" t="s">
+      <c r="E22" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="F22" s="8" t="s">
+      <c r="F22" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="G22" s="8" t="s">
+      <c r="G22" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="H22" s="8" t="s">
+      <c r="H22" s="9" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2125,23 +2170,23 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7" t="s">
+      <c r="B23" s="12"/>
+      <c r="C23" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="D23" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="E23" s="8" t="s">
+      <c r="E23" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="F23" s="8" t="s">
+      <c r="F23" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="G23" s="8" t="s">
+      <c r="G23" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="H23" s="8" t="s">
+      <c r="H23" s="9" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2150,23 +2195,23 @@
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7" t="s">
+      <c r="B24" s="12"/>
+      <c r="C24" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D24" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="E24" s="8" t="s">
+      <c r="E24" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F24" s="8" t="s">
+      <c r="F24" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="G24" s="8" t="s">
+      <c r="G24" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="H24" s="8" t="s">
+      <c r="H24" s="9" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2175,21 +2220,21 @@
         <f t="shared" ref="A25:A36" si="2">ROW()-3</f>
         <v>22</v>
       </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="8" t="s">
+      <c r="B25" s="12"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="E25" s="8" t="s">
+      <c r="E25" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="F25" s="8" t="s">
+      <c r="F25" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="G25" s="8" t="s">
+      <c r="G25" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="H25" s="8" t="s">
+      <c r="H25" s="9" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2198,23 +2243,23 @@
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7" t="s">
+      <c r="B26" s="12"/>
+      <c r="C26" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="D26" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="E26" s="8" t="s">
+      <c r="E26" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="F26" s="8" t="s">
+      <c r="F26" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="G26" s="8" t="s">
+      <c r="G26" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H26" s="8" t="s">
+      <c r="H26" s="9" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2223,23 +2268,23 @@
         <f t="shared" si="2"/>
         <v>24</v>
       </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7" t="s">
+      <c r="B27" s="12"/>
+      <c r="C27" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="D27" s="8" t="s">
+      <c r="D27" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="E27" s="8" t="s">
+      <c r="E27" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="F27" s="8" t="s">
+      <c r="F27" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="G27" s="8" t="s">
+      <c r="G27" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H27" s="8" t="s">
+      <c r="H27" s="9" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2248,23 +2293,23 @@
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="B28" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="C28" s="7"/>
-      <c r="D28" s="8" t="s">
+      <c r="C28" s="12"/>
+      <c r="D28" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="E28" s="8" t="s">
+      <c r="E28" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="F28" s="8" t="s">
+      <c r="F28" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="G28" s="8" t="s">
+      <c r="G28" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="H28" s="8" t="s">
+      <c r="H28" s="9" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2273,21 +2318,21 @@
         <f t="shared" si="2"/>
         <v>26</v>
       </c>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="8" t="s">
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="E29" s="8" t="s">
+      <c r="E29" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="F29" s="8" t="s">
+      <c r="F29" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="G29" s="8" t="s">
+      <c r="G29" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H29" s="8" t="s">
+      <c r="H29" s="9" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2296,25 +2341,25 @@
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="C30" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="D30" s="8" t="s">
+      <c r="D30" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="E30" s="8" t="s">
+      <c r="E30" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="F30" s="8" t="s">
+      <c r="F30" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="G30" s="8" t="s">
+      <c r="G30" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="H30" s="8" t="s">
+      <c r="H30" s="9" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2323,69 +2368,69 @@
         <f t="shared" si="2"/>
         <v>28</v>
       </c>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7" t="s">
+      <c r="B31" s="12"/>
+      <c r="C31" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="D31" s="8" t="s">
+      <c r="D31" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="E31" s="8" t="s">
+      <c r="E31" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F31" s="8" t="s">
+      <c r="F31" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="G31" s="8" t="s">
+      <c r="G31" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="H31" s="8" t="s">
+      <c r="H31" s="9" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="32" ht="15" spans="1:8">
+    <row r="32" ht="15.6" spans="1:8">
       <c r="A32" s="6">
         <v>29</v>
       </c>
-      <c r="B32" s="7"/>
-      <c r="C32" s="9" t="s">
+      <c r="B32" s="12"/>
+      <c r="C32" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="D32" s="8" t="s">
+      <c r="D32" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="E32" s="8" t="s">
+      <c r="E32" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="F32" s="8" t="s">
+      <c r="F32" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="G32" s="8" t="s">
+      <c r="G32" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H32" s="8" t="s">
+      <c r="H32" s="9" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="33" ht="15" spans="1:8">
+    <row r="33" ht="15.6" spans="1:8">
       <c r="A33" s="6">
         <v>30</v>
       </c>
-      <c r="B33" s="7"/>
-      <c r="C33" s="10"/>
-      <c r="D33" s="8" t="s">
+      <c r="B33" s="12"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="E33" s="8" t="s">
+      <c r="E33" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="F33" s="8" t="s">
+      <c r="F33" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="G33" s="8" t="s">
+      <c r="G33" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="H33" s="8" t="s">
+      <c r="H33" s="9" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2394,23 +2439,23 @@
         <f>ROW()-3</f>
         <v>31</v>
       </c>
-      <c r="B34" s="7"/>
-      <c r="C34" s="7" t="s">
+      <c r="B34" s="12"/>
+      <c r="C34" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="D34" s="8" t="s">
+      <c r="D34" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="E34" s="8" t="s">
+      <c r="E34" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="F34" s="8" t="s">
+      <c r="F34" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="G34" s="8" t="s">
+      <c r="G34" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="H34" s="8" t="s">
+      <c r="H34" s="9" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2419,23 +2464,23 @@
         <f>ROW()-3</f>
         <v>32</v>
       </c>
-      <c r="B35" s="7"/>
-      <c r="C35" s="7" t="s">
+      <c r="B35" s="12"/>
+      <c r="C35" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="D35" s="8" t="s">
+      <c r="D35" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="E35" s="8" t="s">
+      <c r="E35" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="F35" s="8" t="s">
+      <c r="F35" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="G35" s="8" t="s">
+      <c r="G35" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="H35" s="8" t="s">
+      <c r="H35" s="9" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2444,23 +2489,23 @@
         <f>ROW()-3</f>
         <v>33</v>
       </c>
-      <c r="B36" s="7"/>
-      <c r="C36" s="7" t="s">
+      <c r="B36" s="12"/>
+      <c r="C36" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="D36" s="8" t="s">
+      <c r="D36" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="E36" s="8" t="s">
+      <c r="E36" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="F36" s="8" t="s">
+      <c r="F36" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="G36" s="8" t="s">
+      <c r="G36" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="H36" s="8" t="s">
+      <c r="H36" s="9" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2469,23 +2514,23 @@
         <f>ROW()-3</f>
         <v>34</v>
       </c>
-      <c r="B37" s="7" t="s">
+      <c r="B37" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="C37" s="7"/>
-      <c r="D37" s="8" t="s">
+      <c r="C37" s="12"/>
+      <c r="D37" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="E37" s="11">
+      <c r="E37" s="15">
         <v>1</v>
       </c>
-      <c r="F37" s="8" t="s">
+      <c r="F37" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="G37" s="8" t="s">
+      <c r="G37" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H37" s="8" t="s">
+      <c r="H37" s="9" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2494,23 +2539,23 @@
         <f>ROW()-3</f>
         <v>35</v>
       </c>
-      <c r="B38" s="7" t="s">
+      <c r="B38" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8" t="s">
+      <c r="C38" s="12"/>
+      <c r="D38" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="E38" s="8" t="s">
+      <c r="E38" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="F38" s="8" t="s">
+      <c r="F38" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="G38" s="8" t="s">
+      <c r="G38" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H38" s="8" t="s">
+      <c r="H38" s="9" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2526,9 +2571,9 @@
     <mergeCell ref="C19:C20"/>
     <mergeCell ref="C24:C25"/>
     <mergeCell ref="C32:C33"/>
+    <mergeCell ref="A1:H2"/>
+    <mergeCell ref="B28:C29"/>
     <mergeCell ref="B4:C7"/>
-    <mergeCell ref="B28:C29"/>
-    <mergeCell ref="A1:H2"/>
   </mergeCells>
   <pageMargins left="0.707638888888889" right="0.511805555555556" top="0.747916666666667" bottom="0.747916666666667" header="0.313888888888889" footer="0.313888888888889"/>
   <pageSetup paperSize="9" scale="92" fitToHeight="0" orientation="landscape"/>

--- a/3-能力管理/运行记录类文件/TXHS-03-03-运维服务能力管理指标体系.xlsx
+++ b/3-能力管理/运行记录类文件/TXHS-03-03-运维服务能力管理指标体系.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="125">
   <si>
     <t xml:space="preserve">运维服务能力管理指标体系       </t>
   </si>
@@ -454,9 +454,6 @@
   </si>
   <si>
     <t>服务数据分析利用次数</t>
-  </si>
-  <si>
-    <t>≥3次</t>
   </si>
   <si>
     <t>数量，服务数据分析使用报告数</t>
@@ -2497,10 +2494,10 @@
         <v>117</v>
       </c>
       <c r="E36" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F36" s="9" t="s">
         <v>118</v>
-      </c>
-      <c r="F36" s="9" t="s">
-        <v>119</v>
       </c>
       <c r="G36" s="9" t="s">
         <v>28</v>
@@ -2515,17 +2512,17 @@
         <v>34</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C37" s="12"/>
       <c r="D37" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E37" s="15">
         <v>1</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G37" s="9" t="s">
         <v>16</v>
@@ -2540,17 +2537,17 @@
         <v>35</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C38" s="12"/>
       <c r="D38" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E38" s="9" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G38" s="9" t="s">
         <v>16</v>
